--- a/selenium-tests/client/addToCartTest.xlsx
+++ b/selenium-tests/client/addToCartTest.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\selenium\flower-shop\selenium-tests\client\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B14E24A-CD7E-408F-89A6-EC9BBC530893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,53 +25,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass/Fail</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Expected result</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>Pass/Fail</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>nguyenquocthang909@gmail.com</t>
+  </si>
+  <si>
+    <t>Aa@123456</t>
+  </si>
+  <si>
+    <t>Thêm vào giỏ hàng hợp lệ</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ hàng thành công!</t>
+  </si>
+  <si>
+    <t>Thêm vào giỏ hàng mà không chọn kích cỡ hoặc màu sắc</t>
+  </si>
+  <si>
+    <t>Vui lòng chọn màu sắc, kích cỡ và số lượng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,7 +86,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -86,99 +94,79 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -231,42 +219,77 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="G1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>

--- a/selenium-tests/client/addToCartTest.xlsx
+++ b/selenium-tests/client/addToCartTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\selenium\flower-shop\selenium-tests\client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B14E24A-CD7E-408F-89A6-EC9BBC530893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF706F2-3C4A-4E3A-B747-123C127648C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t>Thêm sản phẩm vào giỏ hàng thành công!</t>
-  </si>
-  <si>
-    <t>Thêm vào giỏ hàng mà không chọn kích cỡ hoặc màu sắc</t>
-  </si>
-  <si>
-    <t>Vui lòng chọn màu sắc, kích cỡ và số lượng</t>
   </si>
 </sst>
 </file>
@@ -226,7 +220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -267,23 +261,6 @@
       </c>
       <c r="E2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/client/addToCartTest.xlsx
+++ b/selenium-tests/client/addToCartTest.xlsx
@@ -1,51 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\selenium\flower-shop\selenium-tests\client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\web-app-projects\flower-shop-1\selenium-tests\client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF706F2-3C4A-4E3A-B747-123C127648C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0FB560-2B4E-4762-A25E-D5C1A91D22BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Add to Cart Result" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Pre-conditions</t>
+  </si>
+  <si>
+    <t>Steps to reproduce</t>
+  </si>
+  <si>
     <t>Email</t>
   </si>
   <si>
     <t>Password</t>
   </si>
   <si>
-    <t>Expected result</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>Pass/Fail</t>
-  </si>
-  <si>
-    <t>Summary</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>TC_P_1</t>
+  </si>
+  <si>
+    <t>Xem sản phẩm</t>
+  </si>
+  <si>
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa</t>
   </si>
   <si>
     <t>nguyenquocthang909@gmail.com</t>
@@ -54,32 +55,173 @@
     <t>Aa@123456</t>
   </si>
   <si>
-    <t>Thêm vào giỏ hàng hợp lệ</t>
-  </si>
-  <si>
-    <t>Thêm sản phẩm vào giỏ hàng thành công!</t>
+    <t>Danh sách sản phẩm hiển thị đầy đủ</t>
+  </si>
+  <si>
+    <t>Test Summary</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected </t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng bán hoa (localhost:4200)
+3.	Xác nhận trang bán hoa hiển thị thành công
+4.	Xác nhận danh sách sản phẩm hiển thị thành công</t>
+  </si>
+  <si>
+    <t>TC_P_2</t>
+  </si>
+  <si>
+    <t>Xem chi tiết sản phẩm</t>
+  </si>
+  <si>
+    <t>1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng bán hoa (localhost:4200)
+3.	Xác nhận trang bán hoa hiển thị thành công
+4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
+5.	Xác nhận trang chi tiết sản phẩm hiển thị thành công với lựa chọn kích cỡ và màu, cùng với thông tin như tên sản phẩm, giá cả và số tồn kho</t>
+  </si>
+  <si>
+    <t>Aa@123457</t>
+  </si>
+  <si>
+    <t>Trang chi tiết sản phẩm hiển thị thành công</t>
+  </si>
+  <si>
+    <t>TC_P_3</t>
+  </si>
+  <si>
+    <t>Hiển thị thông tin sản phẩm khách hàng muốn mua sau khi chọn kích cỡ và màu</t>
+  </si>
+  <si>
+    <t>1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng bán hoa (localhost:4200)
+3.	Xác nhận trang bán hoa hiển thị thành công
+4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
+5.	Xác nhận trang chi tiết sản phẩm hiển thị thành công
+6.	Chọn kích cỡ và màu ngẫu nhiên theo thứ tự
+7.	Xác nhận thông tin sản phẩm khách hàng muốn mua hiển thị thành công</t>
+  </si>
+  <si>
+    <t>Aa@123458</t>
+  </si>
+  <si>
+    <t>Trang chi tiết sản phẩm hiển thị thông tin sản phẩm khách hàng muốn mua sau khi chọn kích cỡ và màu</t>
+  </si>
+  <si>
+    <t>TC_P_4</t>
+  </si>
+  <si>
+    <t>Hiển thị thông tin sản phẩm khách hàng muốn mua sau khi chọn màu và kích cỡ</t>
+  </si>
+  <si>
+    <t>1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng bán hoa (localhost:4200)
+3.	Xác nhận trang bán hoa hiển thị thành công
+4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
+5.	Xác nhận trang chi tiết sản phẩm hiển thị thành công
+6.	Chọn màu và kích cỡ ngẫu nhiên theo thứ tự
+7.	Xác nhận thông tin sản phẩm khách hàng muốn mua hiển thị thành công</t>
+  </si>
+  <si>
+    <t>Aa@123459</t>
+  </si>
+  <si>
+    <t>Trang chi tiết sản phẩm hiển thị thông tin sản phẩm khách hàng muốn mua sau khi chọn màu và kích cỡ</t>
+  </si>
+  <si>
+    <t>TC_P_5</t>
+  </si>
+  <si>
+    <t>Thông tin sản phẩm khách hàng muốn mua cập nhật sau khi đổi màu</t>
+  </si>
+  <si>
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+Sản phẩm có kích cỡ và màu đa dạng</t>
+  </si>
+  <si>
+    <t>1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng bán hoa (localhost:4200)
+3.	Xác nhận trang bán hoa hiển thị thành công
+4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
+5.	Xác nhận trang chi tiết sản phẩm hiển thị thành công
+6.	Chọn màu khác với lựa chọn hiện tại
+7.	Xác nhận thông tin sản phẩm khách hàng muốn mua hiển thị thành công</t>
+  </si>
+  <si>
+    <t>Aa@123460</t>
+  </si>
+  <si>
+    <t>TC_P_6</t>
+  </si>
+  <si>
+    <t>Thông tin sản phẩm khách hàng muốn mua cập nhật sau khi đổi kích cỡ</t>
+  </si>
+  <si>
+    <t>1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng bán hoa (localhost:4200)
+3.	Xác nhận trang bán hoa hiển thị thành công
+4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
+5.	Xác nhận trang chi tiết sản phẩm hiển thị thành công
+6.	Chọn kích cỡ khác với lựa chọn hiện tại
+7.	Xác nhận thông tin sản phẩm khách hàng muốn mua hiển thị thành công</t>
+  </si>
+  <si>
+    <t>Aa@123461</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -87,18 +229,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Check Cell" xfId="1" builtinId="23"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{22E8A63A-4C76-4BC2-92EC-254C05960060}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -111,164 +353,533 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="LibreOffice">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" ht="330.75" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="4" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
+      <c r="F4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
+  <mergeCells count="8">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/selenium-tests/client/addToCartTest.xlsx
+++ b/selenium-tests/client/addToCartTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\web-app-projects\flower-shop-1\selenium-tests\client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\selenium\flower-shop\selenium-tests\client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0FB560-2B4E-4762-A25E-D5C1A91D22BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C42B5C5-D7D5-497A-A700-1DAA72E01DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Add to Cart Result" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -193,7 +193,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -675,9 +675,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="9"/>
       <c r="C2" s="7"/>
@@ -719,7 +719,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" ht="330.75" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="390.6" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -744,7 +744,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -769,7 +769,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -819,7 +819,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -844,7 +844,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
